--- a/Admin/Course Index.xlsx
+++ b/Admin/Course Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/851caa7714272873/CLASSES-Informatics/Admin/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="14_{A7AB479B-D60E-EA45-B3DD-6B710ED86952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EB099B4-2285-4378-A84A-20346B4A8CE3}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="14_{A7AB479B-D60E-EA45-B3DD-6B710ED86952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65310BB0-4D6D-2347-B2E1-166B7048C942}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="15400" xr2:uid="{FC2EA60D-F956-465D-A12E-C3B3EB9E01DA}"/>
+    <workbookView xWindow="5680" yWindow="2620" windowWidth="27040" windowHeight="16960" xr2:uid="{FC2EA60D-F956-465D-A12E-C3B3EB9E01DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -593,7 +593,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -714,11 +714,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1052,22 +1052,44 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{A72BD2A6-BA92-8346-BAC4-90EC847B8F95}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;0e72c821-16c5-48fd-9e21-120cdafb5e38&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{020239F1-22D1-4A67-97C5-4C81E0D11DBA}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="1" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="28.140625" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="38.140625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="18.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="28.1640625" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="32.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="38.1640625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1085,7 +1107,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1101,7 +1123,7 @@
       </c>
       <c r="G2" s="4"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D3" s="9"/>
       <c r="E3" s="9" t="s">
         <v>9</v>
@@ -1111,7 +1133,7 @@
       </c>
       <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="s">
         <v>11</v>
@@ -1121,7 +1143,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
         <v>13</v>
@@ -1131,7 +1153,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
         <v>15</v>
@@ -1141,7 +1163,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
         <v>17</v>
@@ -1151,7 +1173,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D8" s="9"/>
       <c r="E8" s="9" t="s">
         <v>19</v>
@@ -1161,7 +1183,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D9" s="9"/>
       <c r="E9" s="9" t="s">
         <v>21</v>
@@ -1171,7 +1193,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
         <v>23</v>
@@ -1181,7 +1203,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
         <v>25</v>
       </c>
@@ -1196,7 +1218,7 @@
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E12" s="1" t="s">
         <v>29</v>
       </c>
@@ -1205,7 +1227,7 @@
       </c>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E13" s="1" t="s">
         <v>31</v>
       </c>
@@ -1214,7 +1236,7 @@
       </c>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E14" s="1" t="s">
         <v>33</v>
       </c>
@@ -1223,13 +1245,13 @@
       </c>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E15" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E16" s="1" t="s">
         <v>36</v>
       </c>
@@ -1238,7 +1260,7 @@
       </c>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E17" s="1" t="s">
         <v>38</v>
       </c>
@@ -1247,7 +1269,7 @@
       </c>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E18" s="1" t="s">
         <v>40</v>
       </c>
@@ -1256,7 +1278,7 @@
       </c>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E19" s="1" t="s">
         <v>42</v>
       </c>
@@ -1265,7 +1287,7 @@
       </c>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E20" s="1" t="s">
         <v>44</v>
       </c>
@@ -1274,13 +1296,13 @@
       </c>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E21" s="1" t="s">
         <v>46</v>
       </c>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E22" s="1" t="s">
         <v>47</v>
       </c>
@@ -1289,7 +1311,7 @@
       </c>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E23" s="1" t="s">
         <v>49</v>
       </c>
@@ -1298,7 +1320,7 @@
       </c>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E24" s="1" t="s">
         <v>51</v>
       </c>
@@ -1307,7 +1329,7 @@
       </c>
       <c r="G24" s="4"/>
     </row>
-    <row r="25" spans="1:7" ht="14.1" thickBot="1">
+    <row r="25" spans="1:7" ht="14" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E25" s="1" t="s">
         <v>53</v>
       </c>
@@ -1316,7 +1338,7 @@
       </c>
       <c r="G25" s="4"/>
     </row>
-    <row r="26" spans="1:7" ht="15.95" thickBot="1">
+    <row r="26" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>55</v>
       </c>
@@ -1339,7 +1361,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" thickBot="1">
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D27" s="8" t="s">
         <v>62</v>
       </c>
@@ -1353,7 +1375,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1">
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D28" s="8" t="s">
         <v>66</v>
       </c>
@@ -1365,7 +1387,7 @@
       </c>
       <c r="G28" s="16"/>
     </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1">
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D29" s="8" t="s">
         <v>69</v>
       </c>
@@ -1375,11 +1397,11 @@
       <c r="F29" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="G29" s="17" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="13.5" customHeight="1" thickBot="1">
+    <row r="30" spans="1:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D30" s="8" t="s">
         <v>73</v>
       </c>
@@ -1389,9 +1411,9 @@
       <c r="F30" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="G30" s="15"/>
-    </row>
-    <row r="31" spans="1:7" ht="13.5" customHeight="1" thickBot="1">
+      <c r="G30" s="17"/>
+    </row>
+    <row r="31" spans="1:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D31" s="8" t="s">
         <v>76</v>
       </c>
@@ -1402,7 +1424,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="13.5" customHeight="1" thickBot="1">
+    <row r="32" spans="1:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D32" s="8" t="s">
         <v>79</v>
       </c>
@@ -1413,7 +1435,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="13.5" customHeight="1" thickBot="1">
+    <row r="33" spans="2:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D33" s="8" t="s">
         <v>80</v>
       </c>
@@ -1423,11 +1445,11 @@
       <c r="F33" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="13.5" customHeight="1" thickBot="1">
+    <row r="34" spans="2:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D34" s="8" t="s">
         <v>84</v>
       </c>
@@ -1437,9 +1459,9 @@
       <c r="F34" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="G34" s="15"/>
-    </row>
-    <row r="35" spans="2:7" ht="13.5" customHeight="1" thickBot="1">
+      <c r="G34" s="17"/>
+    </row>
+    <row r="35" spans="2:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D35" s="8" t="s">
         <v>87</v>
       </c>
@@ -1449,11 +1471,11 @@
       <c r="F35" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="G35" s="15" t="s">
+      <c r="G35" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="13.5" customHeight="1" thickBot="1">
+    <row r="36" spans="2:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D36" s="8" t="s">
         <v>91</v>
       </c>
@@ -1461,9 +1483,9 @@
         <v>92</v>
       </c>
       <c r="F36" s="12"/>
-      <c r="G36" s="15"/>
-    </row>
-    <row r="37" spans="2:7" ht="13.5" customHeight="1" thickBot="1">
+      <c r="G36" s="17"/>
+    </row>
+    <row r="37" spans="2:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D37" s="8" t="s">
         <v>93</v>
       </c>
@@ -1473,11 +1495,11 @@
       <c r="F37" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="G37" s="15" t="s">
+      <c r="G37" s="17" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="13.5" customHeight="1" thickBot="1">
+    <row r="38" spans="2:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D38" s="8" t="s">
         <v>97</v>
       </c>
@@ -1487,9 +1509,9 @@
       <c r="F38" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="G38" s="15"/>
-    </row>
-    <row r="39" spans="2:7" ht="13.5" customHeight="1" thickBot="1">
+      <c r="G38" s="17"/>
+    </row>
+    <row r="39" spans="2:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D39" s="8" t="s">
         <v>100</v>
       </c>
@@ -1499,11 +1521,11 @@
       <c r="F39" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G39" s="15" t="s">
+      <c r="G39" s="17" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="2:7" ht="13.5" customHeight="1" thickBot="1">
+    <row r="40" spans="2:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D40" s="8" t="s">
         <v>104</v>
       </c>
@@ -1513,9 +1535,9 @@
       <c r="F40" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="G40" s="15"/>
-    </row>
-    <row r="41" spans="2:7" ht="13.5" customHeight="1" thickBot="1">
+      <c r="G40" s="17"/>
+    </row>
+    <row r="41" spans="2:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>107</v>
       </c>
@@ -1535,7 +1557,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="13.5" customHeight="1" thickBot="1">
+    <row r="42" spans="2:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D42" s="8" t="s">
         <v>113</v>
       </c>
@@ -1549,7 +1571,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="14.85" customHeight="1" thickBot="1">
+    <row r="43" spans="2:7" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D43" s="8" t="s">
         <v>117</v>
       </c>
@@ -1559,11 +1581,11 @@
       <c r="F43" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G43" s="17" t="s">
+      <c r="G43" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="44" spans="2:7" ht="14.85" customHeight="1" thickBot="1">
+    <row r="44" spans="2:7" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D44" s="8" t="s">
         <v>121</v>
       </c>
@@ -1573,9 +1595,9 @@
       <c r="F44" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="G44" s="17"/>
-    </row>
-    <row r="45" spans="2:7" ht="14.85" customHeight="1" thickBot="1">
+      <c r="G44" s="15"/>
+    </row>
+    <row r="45" spans="2:7" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D45" s="8" t="s">
         <v>124</v>
       </c>
@@ -1585,9 +1607,9 @@
       <c r="F45" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="G45" s="17"/>
-    </row>
-    <row r="46" spans="2:7" ht="14.85" customHeight="1" thickBot="1">
+      <c r="G45" s="15"/>
+    </row>
+    <row r="46" spans="2:7" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D46" s="8" t="s">
         <v>127</v>
       </c>
@@ -1597,9 +1619,9 @@
       <c r="F46" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="G46" s="17"/>
-    </row>
-    <row r="47" spans="2:7" ht="14.85" customHeight="1" thickBot="1">
+      <c r="G46" s="15"/>
+    </row>
+    <row r="47" spans="2:7" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D47" s="8" t="s">
         <v>130</v>
       </c>
@@ -1609,9 +1631,9 @@
       <c r="F47" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="G47" s="17"/>
-    </row>
-    <row r="48" spans="2:7" ht="14.85" customHeight="1" thickBot="1">
+      <c r="G47" s="15"/>
+    </row>
+    <row r="48" spans="2:7" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D48" s="8" t="s">
         <v>133</v>
       </c>
@@ -1621,9 +1643,9 @@
       <c r="F48" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="G48" s="17"/>
-    </row>
-    <row r="49" spans="1:7" ht="14.85" customHeight="1" thickBot="1">
+      <c r="G48" s="15"/>
+    </row>
+    <row r="49" spans="1:7" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D49" s="8" t="s">
         <v>136</v>
       </c>
@@ -1637,7 +1659,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="14.85" customHeight="1" thickBot="1">
+    <row r="50" spans="1:7" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D50" s="8" t="s">
         <v>140</v>
       </c>
@@ -1649,7 +1671,7 @@
       </c>
       <c r="G50" s="14"/>
     </row>
-    <row r="51" spans="1:7" ht="14.85" customHeight="1" thickBot="1">
+    <row r="51" spans="1:7" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D51" s="8" t="s">
         <v>143</v>
       </c>
@@ -1661,7 +1683,7 @@
       </c>
       <c r="G51" s="14"/>
     </row>
-    <row r="52" spans="1:7" ht="14.85" customHeight="1" thickBot="1">
+    <row r="52" spans="1:7" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D52" s="8" t="s">
         <v>146</v>
       </c>
@@ -1673,7 +1695,7 @@
       </c>
       <c r="G52" s="14"/>
     </row>
-    <row r="53" spans="1:7" ht="14.85" customHeight="1" thickBot="1">
+    <row r="53" spans="1:7" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D53" s="8" t="s">
         <v>149</v>
       </c>
@@ -1687,7 +1709,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="14.85" customHeight="1" thickBot="1">
+    <row r="54" spans="1:7" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D54" s="8" t="s">
         <v>153</v>
       </c>
@@ -1699,7 +1721,7 @@
       </c>
       <c r="G54" s="14"/>
     </row>
-    <row r="55" spans="1:7" ht="14.85" customHeight="1" thickBot="1">
+    <row r="55" spans="1:7" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D55" s="8" t="s">
         <v>156</v>
       </c>
@@ -1711,7 +1733,7 @@
       </c>
       <c r="G55" s="14"/>
     </row>
-    <row r="56" spans="1:7" ht="15" thickBot="1">
+    <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>159</v>
       </c>
@@ -1725,7 +1747,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15" thickBot="1">
+    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D57" s="3" t="s">
         <v>163</v>
       </c>
@@ -1734,7 +1756,7 @@
       </c>
       <c r="F57" s="10"/>
     </row>
-    <row r="58" spans="1:7" ht="15" thickBot="1">
+    <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D58" s="3" t="s">
         <v>165</v>
       </c>
@@ -1745,7 +1767,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15" thickBot="1">
+    <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D59" s="3" t="s">
         <v>168</v>
       </c>
@@ -1754,7 +1776,7 @@
       </c>
       <c r="F59" s="10"/>
     </row>
-    <row r="60" spans="1:7" ht="15" thickBot="1">
+    <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D60" s="3" t="s">
         <v>169</v>
       </c>
@@ -1765,7 +1787,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15" thickBot="1">
+    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D61" s="3" t="s">
         <v>172</v>
       </c>
@@ -1774,7 +1796,7 @@
       </c>
       <c r="F61" s="10"/>
     </row>
-    <row r="62" spans="1:7" ht="15" thickBot="1">
+    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D62" s="3" t="s">
         <v>173</v>
       </c>
@@ -1785,7 +1807,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15" thickBot="1">
+    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D63" s="3" t="s">
         <v>176</v>
       </c>
@@ -1794,7 +1816,7 @@
       </c>
       <c r="F63" s="10"/>
     </row>
-    <row r="64" spans="1:7" ht="15" thickBot="1">
+    <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D64" s="3" t="s">
         <v>177</v>
       </c>
@@ -1805,7 +1827,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="65" spans="4:6" ht="15" thickBot="1">
+    <row r="65" spans="4:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D65" s="3" t="s">
         <v>180</v>
       </c>
@@ -1847,5 +1869,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7751B9CD-9E19-4086-A54B-943746A99677}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7751B9CD-9E19-4086-A54B-943746A99677}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>